--- a/raw/flows_floods_15yrcomparison.xlsx
+++ b/raw/flows_floods_15yrcomparison.xlsx
@@ -5,28 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5204897_ad_unsw_edu_au1/Documents/Desktop/Honours_UNSW/Assessment/RLE/Flows/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5204897_ad_unsw_edu_au1/Documents/Desktop/Honours_UNSW/Assessment/cumbung_assessment/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="8_{B16CB74F-7F5A-422F-8531-F10FC2AE30B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{033666F6-8D05-4296-9F37-05D585B12830}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="8_{B16CB74F-7F5A-422F-8531-F10FC2AE30B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73CF5C12-7E14-4C04-BAD8-5F7F46D0D93B}"/>
   <bookViews>
-    <workbookView xWindow="9960" yWindow="108" windowWidth="12924" windowHeight="13632" activeTab="2" xr2:uid="{B853E129-E620-4025-A24F-201758402292}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{B853E129-E620-4025-A24F-201758402292}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$19:$E$28</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet2!$A$20:$A$28</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet2!$D$19</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet2!$D$20:$D$28</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet2!$E$19</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet2!$E$20:$E$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -288,6 +280,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF4472C4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -300,6 +297,667 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Flood change in last 50 years (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.6850988267992725E-18"/>
+                  <c:y val="3.5191783075017295E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.074039530719709E-17"/>
+                  <c:y val="3.7705241527740969E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.148079061439418E-17"/>
+                  <c:y val="3.770524152774106E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$20:$A$28</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Great Cumbung</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Booligal wetlands</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Macquarie Marshes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Chowilla Lindsay Walpolla</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hattah Lakes</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Gwydir</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Lowbidgee</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Paroo Overflow Swamps</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Yantabulla</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$20:$D$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-59</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-54</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-58</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-28</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7336-4873-A90F-1506C6E2ED84}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Flow change in last 50 years (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="3.7705241527740969E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="3.5191189297919936E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="3.5191189297920124E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$20:$A$28</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Great Cumbung</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Booligal wetlands</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Macquarie Marshes</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Chowilla Lindsay Walpolla</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Hattah Lakes</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Gwydir</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Lowbidgee</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Paroo Overflow Swamps</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Yantabulla</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$20:$B$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>-58</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-58</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-68</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-47</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-56</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-28</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7336-4873-A90F-1506C6E2ED84}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="315"/>
+        <c:overlap val="-40"/>
+        <c:axId val="162416592"/>
+        <c:axId val="162423664"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="162416592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:glow rad="127000">
+                    <a:schemeClr val="bg1"/>
+                  </a:glow>
+                </a:effectLst>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="162423664"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="162423664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="162416592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -335,7 +993,7 @@
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Flood frequency change over time</a:t>
+              <a:t>Flow frequency change over time</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -378,32 +1036,31 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$D$19</c:f>
+              <c:f>Sheet2!$B$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flood change in last 50 years (%)</c:v>
+                  <c:v>Flow change in last 50 years (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:miter lim="800000"/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -497,43 +1154,43 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$D$20:$D$28</c:f>
+              <c:f>Sheet2!$B$20:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-63</c:v>
+                  <c:v>-58</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-52</c:v>
+                  <c:v>-58</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-59</c:v>
+                  <c:v>-68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-54</c:v>
+                  <c:v>-47</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-50</c:v>
+                  <c:v>-57</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-58</c:v>
+                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-18</c:v>
+                  <c:v>-27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7336-4873-A90F-1506C6E2ED84}"/>
+              <c16:uniqueId val="{00000000-A311-4C55-AE8E-7A846E7B68E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -542,30 +1199,31 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$E$19</c:f>
+              <c:f>Sheet2!$C$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flood change since start of data (%)</c:v>
+                  <c:v>Flow change since start of data (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="bg1">
-                <a:lumMod val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
+            <a:noFill/>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="85000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:miter lim="800000"/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="accent2">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="25000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -659,43 +1317,43 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$E$20:$E$28</c:f>
+              <c:f>Sheet2!$C$20:$C$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-73</c:v>
+                  <c:v>-75</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-74</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-59</c:v>
+                  <c:v>-68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-54</c:v>
+                  <c:v>-58</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-71</c:v>
+                  <c:v>-57</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-58</c:v>
+                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-18</c:v>
+                  <c:v>-27</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-7336-4873-A90F-1506C6E2ED84}"/>
+              <c16:uniqueId val="{00000001-A311-4C55-AE8E-7A846E7B68E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -881,7 +1539,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -917,7 +1575,7 @@
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
               </a:rPr>
-              <a:t>Flow frequency change over time</a:t>
+              <a:t>Flood frequency change over time</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -960,31 +1618,32 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$B$19</c:f>
+              <c:f>Sheet2!$D$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flow change in last 50 years (%)</c:v>
+                  <c:v>Flood change in last 50 years (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="50000"/>
+                <a:lumOff val="50000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:miter lim="800000"/>
             </a:ln>
-            <a:effectLst>
-              <a:glow rad="63500">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="175000"/>
-                  <a:alpha val="25000"/>
-                </a:schemeClr>
-              </a:glow>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -1078,43 +1737,43 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$20:$B$28</c:f>
+              <c:f>Sheet2!$D$20:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-52</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-59</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-54</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-50</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>-58</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-58</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-68</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-47</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-57</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-27</c:v>
+                  <c:v>-18</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A311-4C55-AE8E-7A846E7B68E7}"/>
+              <c16:uniqueId val="{00000000-554D-4532-B375-B2286A168E4A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1123,31 +1782,30 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet2!$C$19</c:f>
+              <c:f>Sheet2!$E$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flow change since start of data (%)</c:v>
+                  <c:v>Flood change since start of data (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:miter lim="800000"/>
             </a:ln>
-            <a:effectLst>
-              <a:glow rad="63500">
-                <a:schemeClr val="accent2">
-                  <a:satMod val="175000"/>
-                  <a:alpha val="25000"/>
-                </a:schemeClr>
-              </a:glow>
-            </a:effectLst>
+            <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -1241,43 +1899,43 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$C$20:$C$28</c:f>
+              <c:f>Sheet2!$E$20:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-75</c:v>
+                  <c:v>-73</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>-74</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-68</c:v>
+                  <c:v>-59</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-54</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-71</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>-58</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-57</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>-28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-27</c:v>
+                  <c:v>-18</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A311-4C55-AE8E-7A846E7B68E7}"/>
+              <c16:uniqueId val="{00000001-554D-4532-B375-B2286A168E4A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1543,6 +2201,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
   <cs:axisTitle>
@@ -2093,6 +2791,555 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="4"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="65000"/>
+                <a:lumOff val="35000"/>
+                <a:alpha val="25000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="213">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2669,243 +3916,33 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8051181" y="5488815"/>
-          <a:ext cx="7611265" cy="5139133"/>
+          <a:off x="8018583" y="5360488"/>
+          <a:ext cx="7581174" cy="5015230"/>
           <a:chOff x="548026" y="5948147"/>
           <a:chExt cx="7566660" cy="5055870"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:grpSp>
-        <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="2" name="Group 1">
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="3" name="Chart 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{221BFE0E-3324-4566-89BA-A77CCC2725EC}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10B26254-1672-4AAD-B4A9-6F2633E0DDA5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvGrpSpPr/>
-        </xdr:nvGrpSpPr>
-        <xdr:grpSpPr>
-          <a:xfrm>
-            <a:off x="548026" y="5948147"/>
-            <a:ext cx="7566660" cy="5055870"/>
-            <a:chOff x="418486" y="1501877"/>
-            <a:chExt cx="7566660" cy="5055870"/>
-          </a:xfrm>
-        </xdr:grpSpPr>
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="3" name="Chart 2">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10B26254-1672-4AAD-B4A9-6F2633E0DDA5}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="418486" y="1501877"/>
-            <a:ext cx="7566660" cy="5055870"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="14" name="Straight Connector 13">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC8B10BB-6936-49FC-A339-BF97BCF0893D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr/>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="763003" y="4933166"/>
-              <a:ext cx="7078980" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="line">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg2">
-                  <a:lumMod val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="1">
-              <a:schemeClr val="accent1"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent1"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-        <xdr:cxnSp macro="">
-          <xdr:nvCxnSpPr>
-            <xdr:cNvPr id="15" name="Straight Connector 14">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65A0B72A-68B8-4376-85D3-EDA446D90E23}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvCxnSpPr/>
-          </xdr:nvCxnSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="755383" y="5119855"/>
-              <a:ext cx="7078980" cy="19050"/>
-            </a:xfrm>
-            <a:prstGeom prst="line">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="1">
-              <a:schemeClr val="accent2"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:schemeClr val="accent2"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:schemeClr val="accent2"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-        </xdr:cxnSp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="16" name="TextBox 15">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B085CE2-54D7-4D29-9A27-7E458488FD73}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6843763" y="4681706"/>
-              <a:ext cx="1080937" cy="264560"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:effectLst/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-AU" sz="1100">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>Average = -39.6</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="17" name="TextBox 16">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55E9F719-AEF9-4128-B6E7-6630A6914E30}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="6851384" y="5108425"/>
-              <a:ext cx="1080937" cy="264560"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-AU" sz="1100">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                </a:rPr>
-                <a:t>Average = -45.6</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </xdr:grpSp>
+          <xdr:cNvGraphicFramePr/>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="548026" y="5948147"/>
+          <a:ext cx="7566660" cy="5055870"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
           <xdr:cNvPr id="20" name="Straight Connector 19">
@@ -2919,7 +3956,7 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="884923" y="7882105"/>
+            <a:off x="875684" y="7671836"/>
             <a:ext cx="7078980" cy="0"/>
           </a:xfrm>
           <a:prstGeom prst="line">
@@ -2987,179 +4024,1417 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>121084</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="11" name="Group 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30276186-0690-4954-9C21-8AA60F4B98C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="15881048" y="5442857"/>
+          <a:ext cx="7581174" cy="5019656"/>
+          <a:chOff x="548026" y="5948147"/>
+          <a:chExt cx="7566660" cy="5055870"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="12" name="Group 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26B34A45-F13C-4487-8207-1D60210FE958}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="548026" y="5948147"/>
+            <a:ext cx="7566660" cy="5055870"/>
+            <a:chOff x="418486" y="1501877"/>
+            <a:chExt cx="7566660" cy="5055870"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="18" name="Chart 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E72D9FB-F234-489E-A8B8-D7AC7B600321}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="418486" y="1501877"/>
+            <a:ext cx="7566660" cy="5055870"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+              <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="19" name="Straight Connector 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B3F7AF-1288-4106-ACE7-C4A6773A955B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="763003" y="4933166"/>
+              <a:ext cx="7078980" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="23" name="Straight Connector 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7210386E-79E8-4403-8578-E84F799B41D6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr/>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="755383" y="5119855"/>
+              <a:ext cx="7078980" cy="19050"/>
+            </a:xfrm>
+            <a:prstGeom prst="line">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="TextBox 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A8C6B87-BC1D-4B99-B364-1E20750F05F6}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6843763" y="4681706"/>
+              <a:ext cx="1080937" cy="264560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:effectLst/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-AU" sz="1100">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Average = -39.6</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="TextBox 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E0D4294-DC4C-4DE7-85E2-3780C76E0776}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="6851384" y="5108425"/>
+              <a:ext cx="1080937" cy="264560"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-AU" sz="1100">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>Average = -45.6</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="13" name="Straight Connector 12">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2847DBE-9968-4D97-8E65-0D2581916C42}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="884923" y="7882105"/>
+            <a:ext cx="7078980" cy="0"/>
+          </a:xfrm>
+          <a:prstGeom prst="line">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>229220</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>126999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>371709</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>61951</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Rectangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E236FDD1-AE6F-4F0C-AB04-66684432A64F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8780553" y="9379856"/>
+          <a:ext cx="142489" cy="660666"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="65000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>538974</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>136292</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>387195</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>176561</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9581E98A-C6BB-4826-9438-8B6767E38159}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8479498" y="9933435"/>
+          <a:ext cx="459030" cy="221697"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="900"/>
+            <a:t>-73</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>32214</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>142487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>174703</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>164619</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D913A8-69E5-4544-82B6-7FE5359104F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8583547" y="9576773"/>
+          <a:ext cx="142489" cy="384989"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>124521</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>3717</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>582961</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>43986</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="TextBox 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9CC2F98-5130-4FA6-B103-554A51DC30B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8675854" y="9982288"/>
+          <a:ext cx="458440" cy="221698"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="900"/>
+            <a:t>-75</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>209394</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>68146</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>351883</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>28946</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0F0C8EE-2503-44EC-853B-55DAFC89E7F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9398218" y="9032852"/>
+          <a:ext cx="142489" cy="857270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>106555</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>156117</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>564995</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>13630</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="TextBox 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56867C46-0B30-484A-8225-ECA62DBBC363}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9295379" y="9837999"/>
+          <a:ext cx="458440" cy="216102"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="900"/>
+            <a:t>-74</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>409498</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>124521</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>551987</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>27878</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D56C6967-4154-4F51-87D0-F803A6DCD6DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9598322" y="9268521"/>
+          <a:ext cx="142489" cy="620533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="65000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>305419</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>159834</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>153640</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>17347</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="TextBox 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF4B252-7BBF-4C26-82E6-BF34246FDC6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9494243" y="9841716"/>
+          <a:ext cx="460809" cy="216102"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="900"/>
+            <a:t>-74</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>562516</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>143107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>94786</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>114611</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09890EDA-CEA5-4ECB-B358-007DEFC8C77F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10976516" y="9107813"/>
+          <a:ext cx="144858" cy="150798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>470209</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>64429</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>318430</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>104698</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="TextBox 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7F9025-4F75-4356-9251-E588DE83357F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10884209" y="9208429"/>
+          <a:ext cx="460809" cy="219563"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="900"/>
+            <a:t>-58</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>332678</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>84873</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>475167</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>61952</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B687DC3A-DE08-4F63-A561-9D3F040BCB3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11971854" y="9228873"/>
+          <a:ext cx="142489" cy="514961"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="65000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>237893</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>11771</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>86114</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>52040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="TextBox 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0D836B-1487-40AD-A10B-6558EED614B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11877069" y="9693653"/>
+          <a:ext cx="460810" cy="219563"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="900"/>
+            <a:t>-71</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>574139</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66053</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>42611</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>140369</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61A9992C-7280-440D-8CC0-284E18B854EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9762963" y="5624171"/>
+          <a:ext cx="81060" cy="74316"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>402533</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>65031</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>481265</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>141391</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{364B9D4F-71B5-4C67-9245-B77BCC7988DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11975408" y="5737419"/>
+          <a:ext cx="78732" cy="76360"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="65000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="65000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>592477</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>147330</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>446171</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>4620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="TextBox 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2326431-83A2-44F6-BB95-CE6C9EDEDC87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9781301" y="5526154"/>
+          <a:ext cx="2304046" cy="215878"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100"/>
+            <a:t>Flood change since start of data (%)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>424035</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>147330</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>277729</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>4620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="TextBox 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FEE322C-4C86-4435-B2CD-59D1BA70A103}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11996910" y="5636738"/>
+          <a:ext cx="2290089" cy="223250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100"/>
+            <a:t>Flow change since start of data (%)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="summary"/>
-      <sheetName val="graph"/>
-      <sheetName val="fourmileweir"/>
-      <sheetName val="corrong"/>
-      <sheetName val="booligal"/>
-      <sheetName val="bool_predCumb"/>
-      <sheetName val="bool_floods_unique"/>
-      <sheetName val="flow2SAdaily"/>
-      <sheetName val="flow2SAmonthly"/>
-      <sheetName val="renmark_dom_PS"/>
-      <sheetName val="chowilla_murrayL10"/>
-      <sheetName val="gwydir_yarra"/>
-      <sheetName val="hattah_barham"/>
-      <sheetName val="hattah_colignan"/>
-      <sheetName val="lowbid_redbank"/>
-      <sheetName val="lowbid_narran"/>
-      <sheetName val="paroo_xing"/>
-      <sheetName val="yanta_corr"/>
-      <sheetName val="yanta_turra"/>
-      <sheetName val="yanta_wyandra"/>
-      <sheetName val="mac_oxley"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>Flood change in last 50 years (%)</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Flood change since start of data (%)</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Gwydir</v>
-          </cell>
-          <cell r="B2">
-            <v>-91</v>
-          </cell>
-          <cell r="C2">
-            <v>-99</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Macquarie Marshes</v>
-          </cell>
-          <cell r="B3">
-            <v>-68</v>
-          </cell>
-          <cell r="C3">
-            <v>-78</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Great Cumbung</v>
-          </cell>
-          <cell r="B4">
-            <v>-67</v>
-          </cell>
-          <cell r="C4">
-            <v>-79</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Booligal wetlands</v>
-          </cell>
-          <cell r="B5">
-            <v>-67</v>
-          </cell>
-          <cell r="C5">
-            <v>-79</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Chowilla Lindsay Walpolla</v>
-          </cell>
-          <cell r="B6">
-            <v>-63</v>
-          </cell>
-          <cell r="C6">
-            <v>-79</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Renmark</v>
-          </cell>
-          <cell r="B7">
-            <v>-63</v>
-          </cell>
-          <cell r="C7">
-            <v>-79</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Hattah Lakes</v>
-          </cell>
-          <cell r="B8">
-            <v>-50</v>
-          </cell>
-          <cell r="C8">
-            <v>-66</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>Lowbidgee</v>
-          </cell>
-          <cell r="B9">
-            <v>-49</v>
-          </cell>
-          <cell r="C9">
-            <v>-65</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>Paroo Overflow Swamps</v>
-          </cell>
-          <cell r="B10">
-            <v>-27</v>
-          </cell>
-          <cell r="C10">
-            <v>-27</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>Yantabulla</v>
-          </cell>
-          <cell r="B11">
-            <v>46</v>
-          </cell>
-          <cell r="C11">
-            <v>46</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/raw/flows_floods_15yrcomparison.xlsx
+++ b/raw/flows_floods_15yrcomparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5204897_ad_unsw_edu_au1/Documents/Desktop/Honours_UNSW/Assessment/cumbung_assessment/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="493" documentId="8_{B16CB74F-7F5A-422F-8531-F10FC2AE30B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73CF5C12-7E14-4C04-BAD8-5F7F46D0D93B}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B8ACA6EC-351E-41E1-8ECA-E48E20AB7765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1849417-9B76-4E46-BB81-687D45661EAE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="1" xr2:uid="{B853E129-E620-4025-A24F-201758402292}"/>
+    <workbookView xWindow="36" yWindow="384" windowWidth="19572" windowHeight="13164" activeTab="1" xr2:uid="{B853E129-E620-4025-A24F-201758402292}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="68">
   <si>
     <t>Dataset_start</t>
   </si>
@@ -203,18 +203,6 @@
     <t>Flow change since start of data (%)</t>
   </si>
   <si>
-    <t>Discharge estimates are from Flows2SA gauge, flood estimates are averaged between Murray L10 and Renmark</t>
-  </si>
-  <si>
-    <t>Estimates are based on Colignan, as it is adjacent to Hattah Lakes (whereas Barham is far away), however, Barham is a longer dataset so has been used for the "all-time" flood change (not for "all-time" flow change, given it has a value smaller than the 50-year flow change for Colignan). (IS THIS OK?)</t>
-  </si>
-  <si>
-    <t>Estimates are all based on Redbank, as Narrandera's data gap prevented its dataset from being much longer than Redbank's anyway</t>
-  </si>
-  <si>
-    <t>The longer dataset (Wyandra) was used for discharge change, but Turra had to be used for flood change as water levels were poorly correlated between the two gauges</t>
-  </si>
-  <si>
     <t>Average</t>
   </si>
   <si>
@@ -237,6 +225,24 @@
   </si>
   <si>
     <t>Flood</t>
+  </si>
+  <si>
+    <t>Great Cumbung Swamp</t>
+  </si>
+  <si>
+    <t>Booligal Wetlands</t>
+  </si>
+  <si>
+    <t>Murray Riverland Wetlands</t>
+  </si>
+  <si>
+    <t>Gwydir Wetlands</t>
+  </si>
+  <si>
+    <t>Lowbidgee Wetlands</t>
+  </si>
+  <si>
+    <t>Yantabulla Swamps</t>
   </si>
 </sst>
 </file>
@@ -333,16 +339,14 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="50000"/>
-                <a:lumOff val="50000"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="65000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:miter lim="800000"/>
@@ -355,8 +359,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-7.6850988267992725E-18"/>
-                  <c:y val="3.5191783075017295E-2"/>
+                  <c:x val="0"/>
+                  <c:y val="5.0380211540781282E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -377,8 +381,8 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-3.074039530719709E-17"/>
-                  <c:y val="3.7705241527740969E-2"/>
+                  <c:x val="0"/>
+                  <c:y val="5.3178019751835906E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -396,11 +400,33 @@
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="5.2918211128901368E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-F6DC-42AF-B25C-BC987152AFA6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-6.148079061439418E-17"/>
-                  <c:y val="3.770524152774106E-2"/>
+                  <c:x val="1.675202283973432E-3"/>
+                  <c:y val="5.5710306406685332E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -414,6 +440,116 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000005-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.675202283973432E-3"/>
+                  <c:y val="5.3178219144485894E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="6.0774879716383894E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.2257597500888447E-16"/>
+                  <c:y val="5.7952301744005182E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="3.770530312168676E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-F6DC-42AF-B25C-BC987152AFA6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.675202283973432E-3"/>
+                  <c:y val="5.064573309698657E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-6CC9-4CA4-948F-62D280390E76}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -431,7 +567,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -476,31 +612,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Great Cumbung</c:v>
+                  <c:v>Booligal Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Booligal wetlands</c:v>
+                  <c:v>Lowbidgee Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Great Cumbung Swamp</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gwydir Wetlands</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Macquarie Marshes</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Chowilla Lindsay Walpolla</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Hattah Lakes</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Gwydir</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>Lowbidgee</c:v>
+                  <c:v>Paroo Overflow Swamps</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Paroo Overflow Swamps</c:v>
+                  <c:v>Murray Riverland Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Yantabulla</c:v>
+                  <c:v>Yantabulla Swamps</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -512,31 +648,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-63</c:v>
+                  <c:v>-92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-52</c:v>
+                  <c:v>-91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-59</c:v>
+                  <c:v>-83</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-54</c:v>
+                  <c:v>-79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-50</c:v>
+                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-58</c:v>
+                  <c:v>-48</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-28</c:v>
+                  <c:v>-31</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-18</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -564,13 +700,13 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="75000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="bg1">
-                  <a:lumMod val="75000"/>
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:miter lim="800000"/>
@@ -583,8 +719,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0"/>
-                  <c:y val="3.7705241527740969E-2"/>
+                  <c:x val="1.675202283973432E-3"/>
+                  <c:y val="6.0515270486099434E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -606,7 +742,7 @@
               <c:layout>
                 <c:manualLayout>
                   <c:x val="0"/>
-                  <c:y val="3.5191189297919936E-2"/>
+                  <c:y val="5.5710306406685235E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -624,11 +760,55 @@
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.1423374177632552E-17"/>
+                  <c:y val="5.0366982172303162E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-F6DC-42AF-B25C-BC987152AFA6}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.675202283973432E-3"/>
+                  <c:y val="5.3178019751836003E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="4"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0"/>
-                  <c:y val="3.5191189297920124E-2"/>
+                  <c:x val="6.1423374177632552E-17"/>
+                  <c:y val="6.330716637123332E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="outEnd"/>
@@ -642,6 +822,94 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000006-0137-486F-AFAF-943D2D0B443E}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="5.5710505799335321E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.2257597500888447E-16"/>
+                  <c:y val="5.5432636450787658E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.228467483552651E-16"/>
+                  <c:y val="5.3178019751835906E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-6CC9-4CA4-948F-62D280390E76}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.2257597500888447E-16"/>
+                  <c:y val="1.5156084336966942E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="outEnd"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-F6DC-42AF-B25C-BC987152AFA6}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -659,7 +927,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -681,20 +949,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="lt1">
-                          <a:lumMod val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -704,31 +959,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Great Cumbung</c:v>
+                  <c:v>Booligal Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Booligal wetlands</c:v>
+                  <c:v>Lowbidgee Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Great Cumbung Swamp</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gwydir Wetlands</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Macquarie Marshes</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Chowilla Lindsay Walpolla</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Hattah Lakes</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Gwydir</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>Lowbidgee</c:v>
+                  <c:v>Paroo Overflow Swamps</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Paroo Overflow Swamps</c:v>
+                  <c:v>Murray Riverland Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Yantabulla</c:v>
+                  <c:v>Yantabulla Swamps</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -740,31 +995,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-58</c:v>
+                  <c:v>-73</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-58</c:v>
+                  <c:v>-41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-68</c:v>
+                  <c:v>-62</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-61</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-37</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>-47</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>-57</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-56</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-28</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-27</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>-72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -794,41 +1049,12 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:effectLst>
-                  <a:glow rad="127000">
-                    <a:schemeClr val="bg1"/>
-                  </a:glow>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="162423664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
@@ -861,7 +1087,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -885,34 +1111,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -1123,31 +1321,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Great Cumbung</c:v>
+                  <c:v>Booligal Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Booligal wetlands</c:v>
+                  <c:v>Lowbidgee Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Great Cumbung Swamp</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gwydir Wetlands</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Macquarie Marshes</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Chowilla Lindsay Walpolla</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Hattah Lakes</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Gwydir</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>Lowbidgee</c:v>
+                  <c:v>Paroo Overflow Swamps</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Paroo Overflow Swamps</c:v>
+                  <c:v>Murray Riverland Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Yantabulla</c:v>
+                  <c:v>Yantabulla Swamps</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1159,31 +1357,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-58</c:v>
+                  <c:v>-73</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-58</c:v>
+                  <c:v>-41</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-68</c:v>
+                  <c:v>-62</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>-67</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-61</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-37</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-63</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>-47</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>-57</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-56</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-28</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-27</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>-72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1286,31 +1484,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Great Cumbung</c:v>
+                  <c:v>Booligal Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Booligal wetlands</c:v>
+                  <c:v>Lowbidgee Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Great Cumbung Swamp</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gwydir Wetlands</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Macquarie Marshes</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Chowilla Lindsay Walpolla</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Hattah Lakes</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Gwydir</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>Lowbidgee</c:v>
+                  <c:v>Paroo Overflow Swamps</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Paroo Overflow Swamps</c:v>
+                  <c:v>Murray Riverland Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Yantabulla</c:v>
+                  <c:v>Yantabulla Swamps</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1322,31 +1520,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-75</c:v>
+                  <c:v>-86</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-74</c:v>
+                  <c:v>-66</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-68</c:v>
+                  <c:v>-71</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-58</c:v>
+                  <c:v>-67</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-57</c:v>
+                  <c:v>-92</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-28</c:v>
+                  <c:v>-63</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-27</c:v>
+                  <c:v>-77</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>15</c:v>
+                  <c:v>-72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1706,31 +1904,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Great Cumbung</c:v>
+                  <c:v>Booligal Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Booligal wetlands</c:v>
+                  <c:v>Lowbidgee Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Great Cumbung Swamp</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gwydir Wetlands</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Macquarie Marshes</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Chowilla Lindsay Walpolla</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Hattah Lakes</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Gwydir</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>Lowbidgee</c:v>
+                  <c:v>Paroo Overflow Swamps</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Paroo Overflow Swamps</c:v>
+                  <c:v>Murray Riverland Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Yantabulla</c:v>
+                  <c:v>Yantabulla Swamps</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1742,31 +1940,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-63</c:v>
+                  <c:v>-92</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-52</c:v>
+                  <c:v>-91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-59</c:v>
+                  <c:v>-83</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-54</c:v>
+                  <c:v>-79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-50</c:v>
+                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-58</c:v>
+                  <c:v>-48</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-28</c:v>
+                  <c:v>-31</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-18</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1868,31 +2066,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Great Cumbung</c:v>
+                  <c:v>Booligal Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Booligal wetlands</c:v>
+                  <c:v>Lowbidgee Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Great Cumbung Swamp</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Gwydir Wetlands</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Macquarie Marshes</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>Chowilla Lindsay Walpolla</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Hattah Lakes</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>Gwydir</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>Lowbidgee</c:v>
+                  <c:v>Paroo Overflow Swamps</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Paroo Overflow Swamps</c:v>
+                  <c:v>Murray Riverland Wetlands</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Yantabulla</c:v>
+                  <c:v>Yantabulla Swamps</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1904,31 +2102,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>-73</c:v>
+                  <c:v>-94</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-74</c:v>
+                  <c:v>-91</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-59</c:v>
+                  <c:v>-88</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-54</c:v>
+                  <c:v>-79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-71</c:v>
+                  <c:v>-56</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-58</c:v>
+                  <c:v>-67</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-28</c:v>
+                  <c:v>-31</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-18</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>25</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3893,15 +4091,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>78059</xdr:colOff>
+      <xdr:colOff>84106</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>99059</xdr:rowOff>
+      <xdr:rowOff>50678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>329519</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>34289</xdr:rowOff>
+      <xdr:colOff>335566</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>167337</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3916,8 +4114,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8018583" y="5360488"/>
-          <a:ext cx="7581174" cy="5015230"/>
+          <a:off x="8042773" y="5339088"/>
+          <a:ext cx="7597921" cy="5040352"/>
           <a:chOff x="548026" y="5948147"/>
           <a:chExt cx="7566660" cy="5055870"/>
         </a:xfrm>
@@ -3956,13 +4154,13 @@
         </xdr:nvCxnSpPr>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="875684" y="7671836"/>
-            <a:ext cx="7078980" cy="0"/>
+            <a:off x="1119355" y="6896843"/>
+            <a:ext cx="6901705" cy="8128"/>
           </a:xfrm>
           <a:prstGeom prst="line">
             <a:avLst/>
           </a:prstGeom>
-          <a:ln>
+          <a:ln w="12700">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -3984,6 +4182,79 @@
         </xdr:style>
       </xdr:cxnSp>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1979</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>58463</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>130256</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>24657</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D56C6967-4154-4F51-87D0-F803A6DCD6DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9797261" y="7899899"/>
+          <a:ext cx="128277" cy="1060348"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="65000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -4050,8 +4321,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15881048" y="5442857"/>
-          <a:ext cx="7581174" cy="5019656"/>
+          <a:off x="15917333" y="5470769"/>
+          <a:ext cx="7597922" cy="5044777"/>
           <a:chOff x="548026" y="5948147"/>
           <a:chExt cx="7566660" cy="5055870"/>
         </a:xfrm>
@@ -4333,15 +4604,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>229220</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>126999</xdr:rowOff>
+      <xdr:colOff>265969</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>59545</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>371709</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>61951</xdr:rowOff>
+      <xdr:colOff>397282</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>156307</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4356,8 +4627,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8780553" y="9379856"/>
-          <a:ext cx="142489" cy="660666"/>
+          <a:off x="8836841" y="9906930"/>
+          <a:ext cx="131313" cy="96762"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4371,146 +4642,7 @@
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-AU" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>538974</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>136292</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>387195</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>176561</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9581E98A-C6BB-4826-9438-8B6767E38159}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8479498" y="9933435"/>
-          <a:ext cx="459030" cy="221697"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-AU" sz="900"/>
-            <a:t>-73</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>32214</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>142487</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>174703</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>164619</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="Rectangle 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D913A8-69E5-4544-82B6-7FE5359104F2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8583547" y="9576773"/>
-          <a:ext cx="142489" cy="384989"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-            <a:alpha val="0"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
+              <a:lumMod val="75000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -4545,22 +4677,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>124521</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>3717</xdr:rowOff>
+      <xdr:colOff>107268</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>95819</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>582961</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>43986</xdr:rowOff>
+      <xdr:colOff>567694</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>136088</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="TextBox 30">
+        <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9CC2F98-5130-4FA6-B103-554A51DC30B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9581E98A-C6BB-4826-9438-8B6767E38159}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4568,8 +4700,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8675854" y="9982288"/>
-          <a:ext cx="458440" cy="221698"/>
+          <a:off x="8678140" y="9943204"/>
+          <a:ext cx="460426" cy="222628"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4598,8 +4730,8 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="900"/>
-            <a:t>-75</a:t>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-94</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4608,16 +4740,154 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>209394</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>453106</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>68146</xdr:rowOff>
+      <xdr:rowOff>41869</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>592666</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>120487</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="Rectangle 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1D913A8-69E5-4544-82B6-7FE5359104F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9023978" y="9159818"/>
+          <a:ext cx="139560" cy="443336"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+            <a:alpha val="0"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>310136</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>52563</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>351883</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>28946</xdr:rowOff>
+      <xdr:colOff>157766</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>92833</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="TextBox 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9CC2F98-5130-4FA6-B103-554A51DC30B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8881008" y="9535230"/>
+          <a:ext cx="459835" cy="222629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-86</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>569927</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>73265</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>91180</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>58615</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4632,8 +4902,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9398218" y="9032852"/>
-          <a:ext cx="142489" cy="857270"/>
+          <a:off x="10365209" y="9555932"/>
+          <a:ext cx="133458" cy="167709"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4647,9 +4917,8 @@
         </a:solidFill>
         <a:ln>
           <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -4684,15 +4953,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>106555</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>156117</xdr:rowOff>
+      <xdr:colOff>466621</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>126345</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>564995</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>13630</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>314252</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>165286</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4707,8 +4976,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9295379" y="9837999"/>
-          <a:ext cx="458440" cy="216102"/>
+          <a:off x="9649698" y="8879576"/>
+          <a:ext cx="459836" cy="221300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4737,8 +5006,8 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="900"/>
-            <a:t>-74</a:t>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-66</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4747,23 +5016,87 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>409498</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>124521</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>416603</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>177977</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>551987</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>27878</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>264823</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>35490</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="Rectangle 33">
+        <xdr:cNvPr id="35" name="TextBox 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D56C6967-4154-4F51-87D0-F803A6DCD6DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF4B252-7BBF-4C26-82E6-BF34246FDC6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10211885" y="9660644"/>
+          <a:ext cx="460425" cy="222231"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-88</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>447059</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>107925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>586154</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>53202</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09890EDA-CEA5-4ECB-B358-007DEFC8C77F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4771,22 +5104,23 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9598322" y="9268521"/>
-          <a:ext cx="142489" cy="620533"/>
+          <a:off x="12078956" y="8678797"/>
+          <a:ext cx="139095" cy="1221790"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
             <a:alpha val="0"/>
           </a:schemeClr>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
+              <a:lumMod val="85000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -4820,23 +5154,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>305419</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>159834</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>295292</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>166773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>153640</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>17347</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>143513</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>25614</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="TextBox 34">
+        <xdr:cNvPr id="38" name="TextBox 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CF4B252-7BBF-4C26-82E6-BF34246FDC6B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7F9025-4F75-4356-9251-E588DE83357F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4844,8 +5178,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9494243" y="9841716"/>
-          <a:ext cx="460809" cy="216102"/>
+          <a:off x="11927189" y="9831799"/>
+          <a:ext cx="460427" cy="223559"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4874,8 +5208,8 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="900"/>
-            <a:t>-74</a:t>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-92</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4885,22 +5219,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>562516</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>143107</xdr:rowOff>
+      <xdr:colOff>149796</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>156050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>94786</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>114611</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>280052</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>174917</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="Rectangle 35">
+        <xdr:cNvPr id="39" name="Rectangle 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09890EDA-CEA5-4ECB-B358-007DEFC8C77F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B687DC3A-DE08-4F63-A561-9D3F040BCB3C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4908,24 +5242,22 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10976516" y="9107813"/>
-          <a:ext cx="144858" cy="150798"/>
+          <a:off x="10557283" y="8726922"/>
+          <a:ext cx="130256" cy="383585"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="65000"/>
             <a:alpha val="0"/>
           </a:schemeClr>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="85000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -4960,22 +5292,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>470209</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>64429</xdr:rowOff>
+      <xdr:colOff>9015</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>101089</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>318430</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>104698</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>469440</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>141357</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="TextBox 37">
+        <xdr:cNvPr id="40" name="TextBox 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D7F9025-4F75-4356-9251-E588DE83357F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0D836B-1487-40AD-A10B-6558EED614B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4983,8 +5315,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10884209" y="9208429"/>
-          <a:ext cx="460809" cy="219563"/>
+          <a:off x="10416502" y="9036679"/>
+          <a:ext cx="460425" cy="222627"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5013,8 +5345,8 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="900"/>
-            <a:t>-58</a:t>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-71</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5023,23 +5355,155 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>332678</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>84873</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>126999</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>18135</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>475167</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>61952</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>96761</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>108849</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="Rectangle 38">
+        <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B687DC3A-DE08-4F63-A561-9D3F040BCB3C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{596B3BCD-BE44-48C4-A552-8DAAE1CAAE45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8678332" y="5823849"/>
+          <a:ext cx="6688667" cy="272143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1600" b="1">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="bg1">
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
+            </a:rPr>
+            <a:t>   B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1600" b="1" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="bg1">
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
+            </a:rPr>
+            <a:t>               </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1600" b="1">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="bg1">
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
+            </a:rPr>
+            <a:t>L</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1600" b="1" baseline="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="bg1">
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
+            </a:rPr>
+            <a:t>              C              G              M             H              P              R                Y             </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-AU" sz="1600" b="1">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:glow rad="63500">
+                <a:schemeClr val="bg1">
+                  <a:alpha val="40000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>609880</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>71641</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>136769</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>71641</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EFFFFF7-5ED0-4581-AF8D-BC18F5C2AABA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5047,22 +5511,23 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11971854" y="9228873"/>
-          <a:ext cx="142489" cy="514961"/>
+          <a:off x="12853983" y="7730718"/>
+          <a:ext cx="139094" cy="729436"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
             <a:alpha val="0"/>
           </a:schemeClr>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
+              <a:lumMod val="85000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -5096,87 +5561,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>237893</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>11771</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>419241</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>158169</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>86114</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>52040</xdr:rowOff>
+      <xdr:colOff>547076</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>57483</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="TextBox 39">
+        <xdr:cNvPr id="45" name="Rectangle 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E0D836B-1487-40AD-A10B-6558EED614B6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11877069" y="9693653"/>
-          <a:ext cx="460810" cy="219563"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-AU" sz="900"/>
-            <a:t>-71</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>574139</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>66053</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>42611</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>140369</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="Rectangle 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61A9992C-7280-440D-8CC0-284E18B854EF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC9756E-7F45-420E-B23D-BE66A9835BB8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5184,8 +5585,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9762963" y="5624171"/>
-          <a:ext cx="81060" cy="74316"/>
+          <a:off x="12663344" y="8181964"/>
+          <a:ext cx="127835" cy="811109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5199,9 +5600,8 @@
         </a:solidFill>
         <a:ln>
           <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="75000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -5235,23 +5635,151 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>402533</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>65031</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>251844</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>175892</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>481265</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>141391</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>100064</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>34732</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="Rectangle 41">
+        <xdr:cNvPr id="46" name="TextBox 45">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{364B9D4F-71B5-4C67-9245-B77BCC7988DF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEFDA050-00D9-4918-8DA6-3A39295DBB0E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12495947" y="8929123"/>
+          <a:ext cx="460425" cy="223558"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-67</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>463324</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>5906</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>311544</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>46175</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="TextBox 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5ABE36E4-6758-49A4-BC08-D7534165CBB5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12707427" y="8394419"/>
+          <a:ext cx="460425" cy="222628"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-56</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>305918</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>113976</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>442872</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>5118</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Rectangle 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A6B6824-BF20-4D3C-A8B9-C27677EF0E3D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5259,22 +5787,23 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11975408" y="5737419"/>
-          <a:ext cx="78732" cy="76360"/>
+          <a:off x="14386636" y="8137771"/>
+          <a:ext cx="136954" cy="1167655"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="bg1">
-            <a:lumMod val="65000"/>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
             <a:alpha val="0"/>
           </a:schemeClr>
         </a:solidFill>
         <a:ln>
           <a:solidFill>
             <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
+              <a:lumMod val="85000"/>
             </a:schemeClr>
           </a:solidFill>
         </a:ln>
@@ -5308,23 +5837,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>592477</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>147330</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>160477</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>127790</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>446171</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>4620</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>597253</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>168060</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="TextBox 42">
+        <xdr:cNvPr id="49" name="TextBox 48">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2326431-83A2-44F6-BB95-CE6C9EDEDC87}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88556A76-21E5-4989-8BF8-3E7241A6BC0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5332,8 +5861,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9781301" y="5526154"/>
-          <a:ext cx="2304046" cy="215878"/>
+          <a:off x="14241195" y="9245739"/>
+          <a:ext cx="436776" cy="222629"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5362,72 +5891,8 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100"/>
-            <a:t>Flood change since start of data (%)</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>424035</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>147330</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>277729</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>4620</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="TextBox 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5FEE322C-4C86-4435-B2CD-59D1BA70A103}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11996910" y="5636738"/>
-          <a:ext cx="2290089" cy="223250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-AU" sz="1100"/>
-            <a:t>Flow change since start of data (%)</a:t>
+            <a:rPr lang="en-AU" sz="1400"/>
+            <a:t>-77</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -6915,193 +7380,181 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B20">
-        <v>-58</v>
+        <v>-73</v>
       </c>
       <c r="C20">
-        <v>-75</v>
+        <v>-86</v>
       </c>
       <c r="D20">
-        <v>-63</v>
+        <v>-92</v>
       </c>
       <c r="E20">
-        <v>-73</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="B21">
-        <v>-58</v>
+        <v>-41</v>
       </c>
       <c r="C21">
-        <v>-74</v>
+        <v>-66</v>
       </c>
       <c r="D21">
-        <v>-52</v>
+        <v>-91</v>
       </c>
       <c r="E21">
-        <v>-74</v>
+        <v>-91</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B22">
-        <v>-68</v>
+        <v>-62</v>
       </c>
       <c r="C22">
-        <v>-68</v>
+        <v>-71</v>
       </c>
       <c r="D22">
-        <v>-59</v>
+        <v>-83</v>
       </c>
       <c r="E22">
-        <v>-59</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B23">
-        <v>-47</v>
+        <v>-67</v>
       </c>
       <c r="C23">
-        <v>-58</v>
+        <v>-67</v>
       </c>
       <c r="D23">
-        <v>-54</v>
+        <v>-79</v>
       </c>
       <c r="E23">
-        <v>-54</v>
+        <v>-79</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B24">
-        <v>-57</v>
+        <v>-61</v>
       </c>
       <c r="C24">
-        <v>-57</v>
+        <v>-92</v>
       </c>
       <c r="D24">
-        <v>-50</v>
+        <v>-56</v>
       </c>
       <c r="E24">
-        <v>-71</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
+        <v>-56</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B25">
-        <v>-56</v>
+        <v>-37</v>
       </c>
       <c r="C25">
         <v>-56</v>
       </c>
       <c r="D25">
-        <v>-58</v>
+        <v>-48</v>
       </c>
       <c r="E25">
-        <v>-58</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26">
-        <v>-28</v>
+        <v>-63</v>
       </c>
       <c r="C26">
-        <v>-28</v>
+        <v>-63</v>
       </c>
       <c r="D26">
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="E26">
-        <v>-28</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
+        <v>-31</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B27">
-        <v>-27</v>
+        <v>-47</v>
       </c>
       <c r="C27">
-        <v>-27</v>
+        <v>-77</v>
       </c>
       <c r="D27">
-        <v>-18</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>-18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>-72</v>
       </c>
       <c r="C28">
-        <v>15</v>
+        <v>-72</v>
       </c>
       <c r="D28">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E28">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B30">
         <f>AVERAGE(B20:B28)</f>
-        <v>-42.666666666666664</v>
+        <v>-58.111111111111114</v>
       </c>
       <c r="C30">
-        <f t="shared" ref="C30:E30" si="0">AVERAGE(C20:C28)</f>
-        <v>-47.555555555555557</v>
+        <f>AVERAGE(C20:C28)</f>
+        <v>-72.222222222222229</v>
       </c>
       <c r="D30">
-        <f t="shared" si="0"/>
-        <v>-39.666666666666664</v>
+        <f t="shared" ref="D30:E30" si="0">AVERAGE(D20:D28)</f>
+        <v>-51.666666666666664</v>
       </c>
       <c r="E30">
         <f t="shared" si="0"/>
-        <v>-45.555555555555557</v>
+        <v>-54.555555555555557</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:E28">
-    <sortCondition ref="C20:C28"/>
+    <sortCondition ref="D20:D28"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7118,13 +7571,13 @@
         <v>40</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -7135,10 +7588,10 @@
         <v>-75</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -7149,10 +7602,10 @@
         <v>-74</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -7163,10 +7616,10 @@
         <v>-68</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -7177,10 +7630,10 @@
         <v>-58</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -7191,10 +7644,10 @@
         <v>-57</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -7205,10 +7658,10 @@
         <v>-56</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -7219,10 +7672,10 @@
         <v>-28</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -7233,10 +7686,10 @@
         <v>-27</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -7247,10 +7700,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -7261,10 +7714,10 @@
         <v>-58</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -7275,10 +7728,10 @@
         <v>-58</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -7289,10 +7742,10 @@
         <v>-68</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -7303,10 +7756,10 @@
         <v>-47</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -7317,10 +7770,10 @@
         <v>-57</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -7331,10 +7784,10 @@
         <v>-56</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -7345,10 +7798,10 @@
         <v>-28</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -7359,10 +7812,10 @@
         <v>-27</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -7373,10 +7826,10 @@
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -7387,10 +7840,10 @@
         <v>-73</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -7401,10 +7854,10 @@
         <v>-74</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -7415,10 +7868,10 @@
         <v>-59</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -7429,10 +7882,10 @@
         <v>-54</v>
       </c>
       <c r="C23" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -7443,10 +7896,10 @@
         <v>-71</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -7457,10 +7910,10 @@
         <v>-58</v>
       </c>
       <c r="C25" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -7471,10 +7924,10 @@
         <v>-28</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -7485,10 +7938,10 @@
         <v>-18</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -7499,10 +7952,10 @@
         <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -7513,10 +7966,10 @@
         <v>-63</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -7527,10 +7980,10 @@
         <v>-52</v>
       </c>
       <c r="C30" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -7541,10 +7994,10 @@
         <v>-59</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -7555,10 +8008,10 @@
         <v>-54</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -7569,10 +8022,10 @@
         <v>-50</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -7583,10 +8036,10 @@
         <v>-58</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -7597,10 +8050,10 @@
         <v>-28</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -7611,10 +8064,10 @@
         <v>-18</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -7625,10 +8078,10 @@
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
